--- a/artfynd/A 40004-2026 artfynd.xlsx
+++ b/artfynd/A 40004-2026 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>136680174</v>
       </c>
       <c r="B5" t="n">
-        <v>9417</v>
+        <v>9418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
